--- a/dbm-ui/backend/ticket/exclusive_ticket.xlsx
+++ b/dbm-ui/backend/ticket/exclusive_ticket.xlsx
@@ -195,7 +195,7 @@
     <t>MySQL 数据构造到已有集群</t>
   </si>
   <si>
-    <t>MySQL 构造回档</t>
+    <t>MySQL 原地构造回档</t>
   </si>
   <si>
     <t>MySQL 单节点迁移</t>
@@ -264,7 +264,7 @@
     <t>TENDBCLUSTER 数据构造到新集群</t>
   </si>
   <si>
-    <t>TENDBCLUSTER 构造回档</t>
+    <t>TENDBCLUSTER 原地构造回档</t>
   </si>
   <si>
     <t>TenDB Cluster 接入 CLB</t>
